--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N128_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N128_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.69157275496068</v>
+        <v>10.02488057268111</v>
       </c>
       <c r="D2" t="n">
-        <v>23.95771181802545</v>
+        <v>3.893128170429136</v>
       </c>
       <c r="E2" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F2" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.25012474217566</v>
+        <v>9.140645270603544</v>
       </c>
       <c r="D3" t="n">
-        <v>15.6144790356757</v>
+        <v>2.537352843297302</v>
       </c>
       <c r="E3" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F3" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.08794765942054</v>
+        <v>8.464291494655839</v>
       </c>
       <c r="D4" t="n">
-        <v>20.954271296889</v>
+        <v>3.405069085744463</v>
       </c>
       <c r="E4" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F4" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.31024726012412</v>
+        <v>6.38791517977017</v>
       </c>
       <c r="D5" t="n">
-        <v>37.66782089743365</v>
+        <v>6.121020895832968</v>
       </c>
       <c r="E5" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F5" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.1205952904584</v>
+        <v>7.494596734699491</v>
       </c>
       <c r="D6" t="n">
-        <v>13.3359969036326</v>
+        <v>2.167099496840298</v>
       </c>
       <c r="E6" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F6" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.16006428171644</v>
+        <v>5.713510445778923</v>
       </c>
       <c r="D7" t="n">
-        <v>30.16344266546281</v>
+        <v>4.901559433137708</v>
       </c>
       <c r="E7" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F7" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.420852117754</v>
+        <v>5.918388469135025</v>
       </c>
       <c r="D8" t="n">
-        <v>18.06890103701508</v>
+        <v>2.93619641851495</v>
       </c>
       <c r="E8" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F8" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.08103169152304</v>
+        <v>5.213167649872495</v>
       </c>
       <c r="D9" t="n">
-        <v>25.81203515245202</v>
+        <v>4.194455712273452</v>
       </c>
       <c r="E9" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F9" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.47794684986684</v>
+        <v>3.490166363103361</v>
       </c>
       <c r="D10" t="n">
-        <v>16.61588784702123</v>
+        <v>2.70008177514095</v>
       </c>
       <c r="E10" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F10" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.32341691299283</v>
+        <v>7.202555248361334</v>
       </c>
       <c r="D11" t="n">
-        <v>38.55636384225902</v>
+        <v>6.265409124367092</v>
       </c>
       <c r="E11" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F11" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.0894010915902</v>
+        <v>7.327027677383408</v>
       </c>
       <c r="D12" t="n">
-        <v>42.5873876089594</v>
+        <v>6.920450486455903</v>
       </c>
       <c r="E12" t="n">
-        <v>10.96839398300708</v>
+        <v>1.782364022238651</v>
       </c>
       <c r="F12" t="n">
-        <v>9.697682781901431</v>
+        <v>1.575873452058983</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
